--- a/data/Omicron_BA1.xlsx
+++ b/data/Omicron_BA1.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\omicron\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive - kanggle\XMU\likangguo\other\github\zhuhai_omicron\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFBC2DF-C457-4E7B-9801-DEDDC7F90B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CF1488-CD75-44FA-BF77-286279DE0587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$P$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -148,6 +148,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -476,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -531,13 +532,13 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -552,16 +553,16 @@
         <v>44571</v>
       </c>
       <c r="H2" s="1">
+        <v>44573</v>
+      </c>
+      <c r="I2" s="1">
+        <v>44574</v>
+      </c>
+      <c r="J2" s="1">
+        <v>44574</v>
+      </c>
+      <c r="K2" s="1">
         <v>44575</v>
-      </c>
-      <c r="I2" s="1">
-        <v>44576</v>
-      </c>
-      <c r="J2" s="1">
-        <v>44577</v>
-      </c>
-      <c r="K2" s="1">
-        <v>44578</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -570,27 +571,27 @@
         <v>18</v>
       </c>
       <c r="N2" s="1">
-        <v>44544</v>
+        <v>44527</v>
       </c>
       <c r="O2">
-        <v>24.58</v>
+        <v>27.97</v>
       </c>
       <c r="P2">
-        <v>24.48</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -602,45 +603,45 @@
         <v>44571</v>
       </c>
       <c r="H3" s="1">
-        <v>44574</v>
+        <v>44572</v>
       </c>
       <c r="I3" s="1">
-        <v>44576</v>
+        <v>44574</v>
       </c>
       <c r="J3" s="1">
-        <v>44579</v>
+        <v>44574</v>
       </c>
       <c r="K3" s="1">
-        <v>44579</v>
+        <v>44575</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" s="1">
-        <v>44528</v>
+        <v>44536</v>
       </c>
       <c r="O3">
-        <v>24.75</v>
+        <v>27.88</v>
       </c>
       <c r="P3">
-        <v>23.42</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -649,45 +650,45 @@
         <v>17</v>
       </c>
       <c r="G4" s="1">
-        <v>44578</v>
+        <v>44569</v>
       </c>
       <c r="H4" s="1">
-        <v>44581</v>
+        <v>44574</v>
       </c>
       <c r="I4" s="1">
-        <v>44581</v>
+        <v>44574</v>
       </c>
       <c r="J4" s="1">
-        <v>44582</v>
+        <v>44574</v>
       </c>
       <c r="K4" s="1">
-        <v>44583</v>
+        <v>44575</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N4" s="1">
-        <v>44342</v>
+        <v>44377</v>
       </c>
       <c r="O4">
-        <v>25.61</v>
+        <v>28.71</v>
       </c>
       <c r="P4">
-        <v>25.19</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -699,45 +700,45 @@
         <v>17</v>
       </c>
       <c r="G5" s="1">
-        <v>44573</v>
+        <v>44568</v>
       </c>
       <c r="H5" s="1">
-        <v>44576</v>
+        <v>44572</v>
       </c>
       <c r="I5" s="1">
-        <v>44581</v>
+        <v>44572</v>
       </c>
       <c r="J5" s="1">
-        <v>44581</v>
+        <v>44574</v>
       </c>
       <c r="K5" s="1">
-        <v>44582</v>
+        <v>44575</v>
       </c>
       <c r="L5">
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N5" s="1">
-        <v>44438</v>
+        <v>44385</v>
       </c>
       <c r="O5">
-        <v>25.72</v>
+        <v>33.159999999999997</v>
       </c>
       <c r="P5">
-        <v>24.22</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -749,48 +750,48 @@
         <v>17</v>
       </c>
       <c r="G6" s="1">
-        <v>44572</v>
+        <v>44565</v>
       </c>
       <c r="H6" s="1">
-        <v>44576</v>
+        <v>44569</v>
       </c>
       <c r="I6" s="1">
-        <v>44579</v>
+        <v>44569</v>
       </c>
       <c r="J6" s="1">
-        <v>44579</v>
+        <v>44575</v>
       </c>
       <c r="K6" s="1">
-        <v>44580</v>
+        <v>44575</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N6" s="1">
-        <v>44476</v>
+        <v>44385</v>
       </c>
       <c r="O6">
-        <v>25.98</v>
+        <v>38.880000000000003</v>
       </c>
       <c r="P6">
-        <v>26.2</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
@@ -799,48 +800,48 @@
         <v>17</v>
       </c>
       <c r="G7" s="1">
-        <v>44571</v>
+        <v>44568</v>
       </c>
       <c r="H7" s="1">
-        <v>44574</v>
+        <v>44572</v>
       </c>
       <c r="I7" s="1">
-        <v>44576</v>
+        <v>44572</v>
       </c>
       <c r="J7" s="1">
-        <v>44576</v>
+        <v>44575</v>
       </c>
       <c r="K7" s="1">
-        <v>44577</v>
+        <v>44575</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="s">
         <v>19</v>
       </c>
       <c r="N7" s="1">
-        <v>44569</v>
+        <v>44536</v>
       </c>
       <c r="O7">
-        <v>26</v>
+        <v>34.28</v>
       </c>
       <c r="P7">
-        <v>24.28</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
@@ -849,48 +850,48 @@
         <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>44573</v>
+        <v>44568</v>
       </c>
       <c r="H8" s="1">
-        <v>44581</v>
+        <v>44572</v>
       </c>
       <c r="I8" s="1">
-        <v>44581</v>
+        <v>44572</v>
       </c>
       <c r="J8" s="1">
-        <v>44582</v>
+        <v>44575</v>
       </c>
       <c r="K8" s="1">
-        <v>44583</v>
+        <v>44575</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" s="1">
-        <v>44325</v>
+        <v>44513</v>
       </c>
       <c r="O8">
-        <v>26.13</v>
+        <v>32.08</v>
       </c>
       <c r="P8">
-        <v>24.6</v>
+        <v>29.61</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
@@ -902,42 +903,42 @@
         <v>44571</v>
       </c>
       <c r="H9" s="1">
-        <v>44574</v>
+        <v>44572</v>
       </c>
       <c r="I9" s="1">
-        <v>44582</v>
+        <v>44575</v>
       </c>
       <c r="J9" s="1">
-        <v>44582</v>
+        <v>44575</v>
       </c>
       <c r="K9" s="1">
-        <v>44583</v>
+        <v>44576</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="1">
-        <v>44549</v>
+        <v>44506</v>
       </c>
       <c r="O9">
-        <v>26.34</v>
+        <v>27.4</v>
       </c>
       <c r="P9">
-        <v>23.41</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -952,42 +953,42 @@
         <v>44571</v>
       </c>
       <c r="H10" s="1">
+        <v>44574</v>
+      </c>
+      <c r="I10" s="1">
         <v>44576</v>
       </c>
-      <c r="I10" s="1">
-        <v>44577</v>
-      </c>
       <c r="J10" s="1">
-        <v>44577</v>
+        <v>44576</v>
       </c>
       <c r="K10" s="1">
         <v>44577</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N10" s="1">
-        <v>44559</v>
+        <v>44526</v>
       </c>
       <c r="O10">
-        <v>26.4</v>
+        <v>32.33</v>
       </c>
       <c r="P10">
-        <v>23.17</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1002,45 +1003,45 @@
         <v>44571</v>
       </c>
       <c r="H11" s="1">
+        <v>44574</v>
+      </c>
+      <c r="I11" s="1">
         <v>44576</v>
       </c>
-      <c r="I11" s="1">
-        <v>44580</v>
-      </c>
       <c r="J11" s="1">
-        <v>44580</v>
+        <v>44576</v>
       </c>
       <c r="K11" s="1">
-        <v>44581</v>
+        <v>44577</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M11" t="s">
         <v>19</v>
       </c>
       <c r="N11" s="1">
-        <v>44541</v>
+        <v>44569</v>
       </c>
       <c r="O11">
-        <v>26.42</v>
+        <v>26</v>
       </c>
       <c r="P11">
-        <v>24.72</v>
+        <v>24.28</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
@@ -1052,45 +1053,45 @@
         <v>44571</v>
       </c>
       <c r="H12" s="1">
-        <v>44574</v>
+        <v>44572</v>
       </c>
       <c r="I12" s="1">
-        <v>44575</v>
+        <v>44574</v>
       </c>
       <c r="J12" s="1">
-        <v>44578</v>
+        <v>44576</v>
       </c>
       <c r="K12" s="1">
-        <v>44579</v>
+        <v>44577</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N12" s="1">
-        <v>44549</v>
+        <v>44536</v>
       </c>
       <c r="O12">
-        <v>26.77</v>
+        <v>31.53</v>
       </c>
       <c r="P12">
-        <v>24.57</v>
+        <v>33.57</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
@@ -1102,42 +1103,42 @@
         <v>44571</v>
       </c>
       <c r="H13" s="1">
-        <v>44574</v>
+        <v>44576</v>
       </c>
       <c r="I13" s="1">
-        <v>44575</v>
+        <v>44577</v>
       </c>
       <c r="J13" s="1">
-        <v>44578</v>
+        <v>44577</v>
       </c>
       <c r="K13" s="1">
-        <v>44579</v>
+        <v>44577</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N13" s="1">
-        <v>44549</v>
+        <v>44559</v>
       </c>
       <c r="O13">
-        <v>26.77</v>
+        <v>26.4</v>
       </c>
       <c r="P13">
-        <v>24.57</v>
+        <v>23.17</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
@@ -1149,40 +1150,45 @@
         <v>17</v>
       </c>
       <c r="G14" s="1">
-        <v>44571</v>
+        <v>44568</v>
       </c>
       <c r="H14" s="1">
-        <v>44578</v>
+        <v>44574</v>
       </c>
       <c r="I14" s="1">
-        <v>44579</v>
+        <v>44576</v>
       </c>
       <c r="J14" s="1">
-        <v>44580</v>
+        <v>44577</v>
       </c>
       <c r="K14" s="1">
-        <v>44581</v>
+        <v>44577</v>
       </c>
       <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="1">
+        <v>44352</v>
+      </c>
       <c r="O14">
-        <v>27.06</v>
+        <v>29.48</v>
       </c>
       <c r="P14">
-        <v>25.41</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
       <c r="C15">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -1197,42 +1203,42 @@
         <v>44571</v>
       </c>
       <c r="H15" s="1">
-        <v>44572</v>
+        <v>44574</v>
       </c>
       <c r="I15" s="1">
         <v>44575</v>
       </c>
       <c r="J15" s="1">
-        <v>44575</v>
+        <v>44577</v>
       </c>
       <c r="K15" s="1">
-        <v>44576</v>
+        <v>44578</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" t="s">
         <v>19</v>
       </c>
       <c r="N15" s="1">
-        <v>44506</v>
+        <v>44565</v>
       </c>
       <c r="O15">
-        <v>27.4</v>
+        <v>26.83</v>
       </c>
       <c r="P15">
-        <v>26.6</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
@@ -1241,48 +1247,48 @@
         <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1">
         <v>44571</v>
       </c>
       <c r="H16" s="1">
-        <v>44574</v>
+        <v>44575</v>
       </c>
       <c r="I16" s="1">
+        <v>44576</v>
+      </c>
+      <c r="J16" s="1">
+        <v>44577</v>
+      </c>
+      <c r="K16" s="1">
         <v>44578</v>
       </c>
-      <c r="J16" s="1">
-        <v>44579</v>
-      </c>
-      <c r="K16" s="1">
-        <v>44579</v>
-      </c>
       <c r="L16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N16" s="1">
-        <v>44379</v>
+        <v>44544</v>
       </c>
       <c r="O16">
-        <v>27.6</v>
+        <v>24.58</v>
       </c>
       <c r="P16">
-        <v>29.78</v>
+        <v>24.48</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -1300,36 +1306,31 @@
         <v>44572</v>
       </c>
       <c r="I17" s="1">
-        <v>44574</v>
+        <v>44576</v>
       </c>
       <c r="J17" s="1">
-        <v>44574</v>
+        <v>44578</v>
       </c>
       <c r="K17" s="1">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="L17">
-        <v>2</v>
-      </c>
-      <c r="M17" t="s">
-        <v>19</v>
-      </c>
-      <c r="N17" s="1">
-        <v>44536</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N17" s="1"/>
       <c r="O17">
-        <v>27.88</v>
+        <v>27.93</v>
       </c>
       <c r="P17">
-        <v>26.8</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -1350,7 +1351,7 @@
         <v>44572</v>
       </c>
       <c r="I18" s="1">
-        <v>44576</v>
+        <v>44575</v>
       </c>
       <c r="J18" s="1">
         <v>44578</v>
@@ -1359,25 +1360,30 @@
         <v>44578</v>
       </c>
       <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="M18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" s="1">
+        <v>44536</v>
+      </c>
       <c r="O18">
-        <v>27.93</v>
+        <v>36.1</v>
       </c>
       <c r="P18">
-        <v>28.04</v>
+        <v>36.299999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19">
         <v>1</v>
-      </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19">
-        <v>53</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
@@ -1392,42 +1398,31 @@
         <v>44571</v>
       </c>
       <c r="H19" s="1">
-        <v>44573</v>
+        <v>44575</v>
       </c>
       <c r="I19" s="1">
-        <v>44574</v>
+        <v>44576</v>
       </c>
       <c r="J19" s="1">
-        <v>44574</v>
+        <v>44578</v>
       </c>
       <c r="K19" s="1">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="L19">
-        <v>3</v>
-      </c>
-      <c r="M19" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" s="1">
-        <v>44527</v>
-      </c>
-      <c r="O19">
-        <v>27.97</v>
-      </c>
-      <c r="P19">
-        <v>25.55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C20">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
@@ -1439,7 +1434,7 @@
         <v>17</v>
       </c>
       <c r="G20" s="1">
-        <v>44574</v>
+        <v>44571</v>
       </c>
       <c r="H20" s="1">
         <v>44574</v>
@@ -1448,39 +1443,39 @@
         <v>44577</v>
       </c>
       <c r="J20" s="1">
-        <v>44579</v>
+        <v>44578</v>
       </c>
       <c r="K20" s="1">
         <v>44579</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M20" t="s">
         <v>19</v>
       </c>
       <c r="N20" s="1">
-        <v>44541</v>
+        <v>44513</v>
       </c>
       <c r="O20">
-        <v>28.31</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="P20">
-        <v>30.58</v>
+        <v>29.74</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
       <c r="C21">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
@@ -1489,16 +1484,16 @@
         <v>17</v>
       </c>
       <c r="G21" s="1">
-        <v>44574</v>
+        <v>44571</v>
       </c>
       <c r="H21" s="1">
         <v>44574</v>
       </c>
       <c r="I21" s="1">
-        <v>44577</v>
+        <v>44575</v>
       </c>
       <c r="J21" s="1">
-        <v>44579</v>
+        <v>44578</v>
       </c>
       <c r="K21" s="1">
         <v>44579</v>
@@ -1507,77 +1502,77 @@
         <v>3</v>
       </c>
       <c r="M21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N21" s="1">
-        <v>44541</v>
+        <v>44549</v>
       </c>
       <c r="O21">
-        <v>28.31</v>
+        <v>26.77</v>
       </c>
       <c r="P21">
-        <v>30.58</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
       </c>
       <c r="C22">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
         <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G22" s="1">
-        <v>44569</v>
+        <v>44571</v>
       </c>
       <c r="H22" s="1">
         <v>44574</v>
       </c>
       <c r="I22" s="1">
-        <v>44574</v>
+        <v>44578</v>
       </c>
       <c r="J22" s="1">
-        <v>44574</v>
+        <v>44579</v>
       </c>
       <c r="K22" s="1">
-        <v>44575</v>
+        <v>44579</v>
       </c>
       <c r="L22">
         <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N22" s="1">
-        <v>44377</v>
+        <v>44379</v>
       </c>
       <c r="O22">
-        <v>28.71</v>
+        <v>27.6</v>
       </c>
       <c r="P22">
-        <v>30.26</v>
+        <v>29.78</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
       <c r="C23">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
         <v>15</v>
@@ -1589,45 +1584,45 @@
         <v>17</v>
       </c>
       <c r="G23" s="1">
-        <v>44571</v>
+        <v>44574</v>
       </c>
       <c r="H23" s="1">
-        <v>44576</v>
+        <v>44574</v>
       </c>
       <c r="I23" s="1">
-        <v>44579</v>
+        <v>44577</v>
       </c>
       <c r="J23" s="1">
         <v>44579</v>
       </c>
       <c r="K23" s="1">
-        <v>44580</v>
+        <v>44579</v>
       </c>
       <c r="L23">
         <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N23" s="1">
-        <v>44542</v>
+        <v>44541</v>
       </c>
       <c r="O23">
-        <v>29.38</v>
+        <v>28.31</v>
       </c>
       <c r="P23">
-        <v>30</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C24">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
@@ -1639,45 +1634,45 @@
         <v>17</v>
       </c>
       <c r="G24" s="1">
-        <v>44571</v>
+        <v>44574</v>
       </c>
       <c r="H24" s="1">
-        <v>44576</v>
+        <v>44574</v>
       </c>
       <c r="I24" s="1">
-        <v>44579</v>
+        <v>44578</v>
       </c>
       <c r="J24" s="1">
         <v>44579</v>
       </c>
       <c r="K24" s="1">
-        <v>44580</v>
+        <v>44579</v>
       </c>
       <c r="L24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N24" s="1">
-        <v>44542</v>
+        <v>44536</v>
       </c>
       <c r="O24">
-        <v>29.38</v>
+        <v>35.92</v>
       </c>
       <c r="P24">
-        <v>30</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
       </c>
       <c r="C25">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D25" t="s">
         <v>23</v>
@@ -1689,7 +1684,7 @@
         <v>17</v>
       </c>
       <c r="G25" s="1">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H25" s="1">
         <v>44574</v>
@@ -1698,10 +1693,10 @@
         <v>44576</v>
       </c>
       <c r="J25" s="1">
-        <v>44577</v>
+        <v>44579</v>
       </c>
       <c r="K25" s="1">
-        <v>44577</v>
+        <v>44579</v>
       </c>
       <c r="L25">
         <v>1</v>
@@ -1710,18 +1705,18 @@
         <v>19</v>
       </c>
       <c r="N25" s="1">
-        <v>44352</v>
+        <v>44528</v>
       </c>
       <c r="O25">
-        <v>29.48</v>
+        <v>24.75</v>
       </c>
       <c r="P25">
-        <v>28.67</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1730,13 +1725,13 @@
         <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
         <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G26" s="1">
         <v>44568</v>
@@ -1745,42 +1740,42 @@
         <v>44574</v>
       </c>
       <c r="I26" s="1">
-        <v>44576</v>
+        <v>44579</v>
       </c>
       <c r="J26" s="1">
-        <v>44577</v>
+        <v>44579</v>
       </c>
       <c r="K26" s="1">
-        <v>44577</v>
+        <v>44579</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="s">
         <v>19</v>
       </c>
       <c r="N26" s="1">
-        <v>44352</v>
+        <v>44349</v>
       </c>
       <c r="O26">
-        <v>29.48</v>
+        <v>39.42</v>
       </c>
       <c r="P26">
-        <v>28.67</v>
+        <v>37.51</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C27">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
         <v>16</v>
@@ -1789,90 +1784,95 @@
         <v>17</v>
       </c>
       <c r="G27" s="1">
-        <v>44577</v>
+        <v>44571</v>
       </c>
       <c r="H27" s="1">
+        <v>44576</v>
+      </c>
+      <c r="I27" s="1">
+        <v>44579</v>
+      </c>
+      <c r="J27" s="1">
+        <v>44579</v>
+      </c>
+      <c r="K27" s="1">
         <v>44580</v>
-      </c>
-      <c r="I27" s="1">
-        <v>44580</v>
-      </c>
-      <c r="J27" s="1">
-        <v>44582</v>
-      </c>
-      <c r="K27" s="1">
-        <v>44583</v>
       </c>
       <c r="L27">
         <v>3</v>
       </c>
       <c r="M27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N27" s="1">
-        <v>44561</v>
+        <v>44542</v>
       </c>
       <c r="O27">
-        <v>30.63</v>
+        <v>29.38</v>
       </c>
       <c r="P27">
-        <v>31.13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>21</v>
       </c>
       <c r="C28">
+        <v>41</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="1">
+        <v>44572</v>
+      </c>
+      <c r="H28" s="1">
+        <v>44576</v>
+      </c>
+      <c r="I28" s="1">
+        <v>44579</v>
+      </c>
+      <c r="J28" s="1">
+        <v>44579</v>
+      </c>
+      <c r="K28" s="1">
+        <v>44580</v>
+      </c>
+      <c r="L28">
         <v>3</v>
       </c>
-      <c r="D28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="1">
-        <v>44573</v>
-      </c>
-      <c r="H28" s="1">
-        <v>44574</v>
-      </c>
-      <c r="I28" s="1">
-        <v>44580</v>
-      </c>
-      <c r="J28" s="1">
-        <v>44580</v>
-      </c>
-      <c r="K28" s="1">
-        <v>44581</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1"/>
+      <c r="M28" t="s">
+        <v>19</v>
+      </c>
+      <c r="N28" s="1">
+        <v>44476</v>
+      </c>
       <c r="O28">
-        <v>31.43</v>
+        <v>25.98</v>
       </c>
       <c r="P28">
-        <v>32.93</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
@@ -1887,45 +1887,45 @@
         <v>44571</v>
       </c>
       <c r="H29" s="1">
-        <v>44572</v>
+        <v>44574</v>
       </c>
       <c r="I29" s="1">
-        <v>44574</v>
+        <v>44578</v>
       </c>
       <c r="J29" s="1">
-        <v>44576</v>
+        <v>44579</v>
       </c>
       <c r="K29" s="1">
-        <v>44577</v>
+        <v>44580</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M29" t="s">
         <v>19</v>
       </c>
       <c r="N29" s="1">
-        <v>44536</v>
+        <v>44558</v>
       </c>
       <c r="O29">
-        <v>31.53</v>
+        <v>36.020000000000003</v>
       </c>
       <c r="P29">
-        <v>33.57</v>
+        <v>34.68</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>21</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E30" t="s">
         <v>16</v>
@@ -1934,45 +1934,40 @@
         <v>17</v>
       </c>
       <c r="G30" s="1">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H30" s="1">
-        <v>44572</v>
+        <v>44578</v>
       </c>
       <c r="I30" s="1">
-        <v>44572</v>
+        <v>44579</v>
       </c>
       <c r="J30" s="1">
-        <v>44575</v>
+        <v>44580</v>
       </c>
       <c r="K30" s="1">
-        <v>44575</v>
+        <v>44581</v>
       </c>
       <c r="L30">
-        <v>1</v>
-      </c>
-      <c r="M30" t="s">
-        <v>19</v>
-      </c>
-      <c r="N30" s="1">
-        <v>44513</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N30" s="1"/>
       <c r="O30">
-        <v>32.08</v>
+        <v>27.06</v>
       </c>
       <c r="P30">
-        <v>29.61</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
       </c>
       <c r="C31">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
         <v>15</v>
@@ -1987,43 +1982,43 @@
         <v>44571</v>
       </c>
       <c r="H31" s="1">
-        <v>44574</v>
+        <v>44576</v>
       </c>
       <c r="I31" s="1">
-        <v>44576</v>
+        <v>44580</v>
       </c>
       <c r="J31" s="1">
-        <v>44576</v>
+        <v>44580</v>
       </c>
       <c r="K31" s="1">
-        <v>44577</v>
+        <v>44581</v>
       </c>
       <c r="L31">
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N31" s="1">
-        <v>44526</v>
+        <v>44541</v>
       </c>
       <c r="O31">
-        <v>32.33</v>
+        <v>26.42</v>
       </c>
       <c r="P31">
-        <v>29.27</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32">
         <v>4</v>
       </c>
-      <c r="B32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32">
-        <v>36</v>
-      </c>
       <c r="D32" t="s">
         <v>15</v>
       </c>
@@ -2034,48 +2029,48 @@
         <v>17</v>
       </c>
       <c r="G32" s="1">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H32" s="1">
-        <v>44572</v>
+        <v>44574</v>
       </c>
       <c r="I32" s="1">
-        <v>44572</v>
+        <v>44580</v>
       </c>
       <c r="J32" s="1">
-        <v>44574</v>
+        <v>44580</v>
       </c>
       <c r="K32" s="1">
-        <v>44575</v>
+        <v>44581</v>
       </c>
       <c r="L32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N32" s="1">
-        <v>44385</v>
+        <v>44570</v>
       </c>
       <c r="O32">
-        <v>33.159999999999997</v>
+        <v>28.312000000000001</v>
       </c>
       <c r="P32">
-        <v>31.5</v>
+        <v>28.946000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C33">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
         <v>16</v>
@@ -2084,54 +2079,49 @@
         <v>17</v>
       </c>
       <c r="G33" s="1">
-        <v>44568</v>
+        <v>44573</v>
       </c>
       <c r="H33" s="1">
-        <v>44572</v>
+        <v>44574</v>
       </c>
       <c r="I33" s="1">
-        <v>44572</v>
+        <v>44580</v>
       </c>
       <c r="J33" s="1">
-        <v>44575</v>
+        <v>44580</v>
       </c>
       <c r="K33" s="1">
-        <v>44575</v>
+        <v>44581</v>
       </c>
       <c r="L33">
-        <v>2</v>
-      </c>
-      <c r="M33" t="s">
-        <v>19</v>
-      </c>
-      <c r="N33" s="1">
-        <v>44536</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N33" s="1"/>
       <c r="O33">
-        <v>34.28</v>
+        <v>31.43</v>
       </c>
       <c r="P33">
-        <v>30.9</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G34" s="1">
         <v>44571</v>
@@ -2140,39 +2130,34 @@
         <v>44574</v>
       </c>
       <c r="I34" s="1">
-        <v>44577</v>
+        <v>44581</v>
       </c>
       <c r="J34" s="1">
-        <v>44578</v>
+        <v>44581</v>
       </c>
       <c r="K34" s="1">
-        <v>44579</v>
+        <v>44581</v>
       </c>
       <c r="L34">
-        <v>1</v>
-      </c>
-      <c r="M34" t="s">
-        <v>19</v>
-      </c>
-      <c r="N34" s="1">
-        <v>44513</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N34" s="1"/>
       <c r="O34">
-        <v>34.299999999999997</v>
+        <v>36.25</v>
       </c>
       <c r="P34">
-        <v>29.74</v>
+        <v>36.159999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>21</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2184,48 +2169,48 @@
         <v>17</v>
       </c>
       <c r="G35" s="1">
-        <v>44571</v>
+        <v>44573</v>
       </c>
       <c r="H35" s="1">
-        <v>44574</v>
+        <v>44576</v>
       </c>
       <c r="I35" s="1">
-        <v>44578</v>
+        <v>44581</v>
       </c>
       <c r="J35" s="1">
-        <v>44579</v>
+        <v>44581</v>
       </c>
       <c r="K35" s="1">
-        <v>44580</v>
+        <v>44582</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M35" t="s">
         <v>19</v>
       </c>
       <c r="N35" s="1">
-        <v>44558</v>
+        <v>44438</v>
       </c>
       <c r="O35">
-        <v>36.020000000000003</v>
+        <v>25.72</v>
       </c>
       <c r="P35">
-        <v>34.68</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
         <v>16</v>
@@ -2234,90 +2219,95 @@
         <v>17</v>
       </c>
       <c r="G36" s="1">
-        <v>44571</v>
+        <v>44573</v>
       </c>
       <c r="H36" s="1">
-        <v>44572</v>
+        <v>44581</v>
       </c>
       <c r="I36" s="1">
-        <v>44575</v>
+        <v>44581</v>
       </c>
       <c r="J36" s="1">
-        <v>44578</v>
+        <v>44582</v>
       </c>
       <c r="K36" s="1">
-        <v>44578</v>
+        <v>44583</v>
       </c>
       <c r="L36">
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N36" s="1">
-        <v>44536</v>
+        <v>44325</v>
       </c>
       <c r="O36">
-        <v>36.1</v>
+        <v>26.13</v>
       </c>
       <c r="P36">
-        <v>36.299999999999997</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s">
         <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G37" s="1">
-        <v>44571</v>
+        <v>44578</v>
       </c>
       <c r="H37" s="1">
-        <v>44574</v>
+        <v>44581</v>
       </c>
       <c r="I37" s="1">
         <v>44581</v>
       </c>
       <c r="J37" s="1">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="K37" s="1">
-        <v>44581</v>
+        <v>44583</v>
       </c>
       <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="N37" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="M37" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" s="1">
+        <v>44342</v>
+      </c>
       <c r="O37">
-        <v>36.25</v>
+        <v>25.61</v>
       </c>
       <c r="P37">
-        <v>36.159999999999997</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C38">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
         <v>23</v>
@@ -2329,48 +2319,48 @@
         <v>17</v>
       </c>
       <c r="G38" s="1">
-        <v>44565</v>
+        <v>44577</v>
       </c>
       <c r="H38" s="1">
-        <v>44569</v>
+        <v>44580</v>
       </c>
       <c r="I38" s="1">
-        <v>44569</v>
+        <v>44580</v>
       </c>
       <c r="J38" s="1">
-        <v>44575</v>
+        <v>44582</v>
       </c>
       <c r="K38" s="1">
-        <v>44575</v>
+        <v>44583</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M38" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N38" s="1">
-        <v>44385</v>
+        <v>44561</v>
       </c>
       <c r="O38">
-        <v>38.880000000000003</v>
+        <v>30.63</v>
       </c>
       <c r="P38">
-        <v>37.49</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
       </c>
       <c r="C39">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E39" t="s">
         <v>16</v>
@@ -2385,13 +2375,13 @@
         <v>44574</v>
       </c>
       <c r="I39" s="1">
-        <v>44575</v>
+        <v>44582</v>
       </c>
       <c r="J39" s="1">
-        <v>44577</v>
+        <v>44582</v>
       </c>
       <c r="K39" s="1">
-        <v>44578</v>
+        <v>44583</v>
       </c>
       <c r="L39">
         <v>2</v>
@@ -2400,208 +2390,19 @@
         <v>19</v>
       </c>
       <c r="N39" s="1">
-        <v>44565</v>
+        <v>44549</v>
       </c>
       <c r="O39">
-        <v>26.83</v>
+        <v>26.34</v>
       </c>
       <c r="P39">
-        <v>24.69</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>18</v>
-      </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" t="s">
-        <v>16</v>
-      </c>
-      <c r="F40" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40" s="1">
-        <v>44571</v>
-      </c>
-      <c r="H40" s="1">
-        <v>44575</v>
-      </c>
-      <c r="I40" s="1">
-        <v>44576</v>
-      </c>
-      <c r="J40" s="1">
-        <v>44578</v>
-      </c>
-      <c r="K40" s="1">
-        <v>44578</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>23</v>
-      </c>
-      <c r="B41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41">
-        <v>8</v>
-      </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" t="s">
-        <v>16</v>
-      </c>
-      <c r="F41" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" s="1">
-        <v>44574</v>
-      </c>
-      <c r="H41" s="1">
-        <v>44574</v>
-      </c>
-      <c r="I41" s="1">
-        <v>44578</v>
-      </c>
-      <c r="J41" s="1">
-        <v>44579</v>
-      </c>
-      <c r="K41" s="1">
-        <v>44579</v>
-      </c>
-      <c r="L41">
-        <v>2</v>
-      </c>
-      <c r="M41" t="s">
-        <v>19</v>
-      </c>
-      <c r="N41" s="1">
-        <v>44536</v>
-      </c>
-      <c r="O41">
-        <v>35.92</v>
-      </c>
-      <c r="P41">
-        <v>36.96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>25</v>
-      </c>
-      <c r="B42" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42">
-        <v>33</v>
-      </c>
-      <c r="D42" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" t="s">
-        <v>16</v>
-      </c>
-      <c r="F42" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="1">
-        <v>44568</v>
-      </c>
-      <c r="H42" s="1">
-        <v>44574</v>
-      </c>
-      <c r="I42" s="1">
-        <v>44579</v>
-      </c>
-      <c r="J42" s="1">
-        <v>44579</v>
-      </c>
-      <c r="K42" s="1">
-        <v>44579</v>
-      </c>
-      <c r="L42">
-        <v>2</v>
-      </c>
-      <c r="M42" t="s">
-        <v>19</v>
-      </c>
-      <c r="N42" s="1">
-        <v>44349</v>
-      </c>
-      <c r="O42">
-        <v>39.42</v>
-      </c>
-      <c r="P42">
-        <v>37.51</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>31</v>
-      </c>
-      <c r="B43" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="1">
-        <v>44571</v>
-      </c>
-      <c r="H43" s="1">
-        <v>44574</v>
-      </c>
-      <c r="I43" s="1">
-        <v>44580</v>
-      </c>
-      <c r="J43" s="1">
-        <v>44580</v>
-      </c>
-      <c r="K43" s="1">
-        <v>44581</v>
-      </c>
-      <c r="L43">
-        <v>1</v>
-      </c>
-      <c r="M43" t="s">
-        <v>19</v>
-      </c>
-      <c r="N43" s="1">
-        <v>44570</v>
-      </c>
-      <c r="O43">
-        <v>28.312000000000001</v>
-      </c>
-      <c r="P43">
-        <v>28.946000000000002</v>
+        <v>23.41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P43" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P43">
-      <sortCondition ref="O1:O43"/>
+  <autoFilter ref="A1:P39" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P39">
+      <sortCondition ref="A1:A39"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
